--- a/DBHYDRO/Shared_data/CR_Flow.xlsx
+++ b/DBHYDRO/Shared_data/CR_Flow.xlsx
@@ -17212,6 +17212,8399 @@
         <v>2415</v>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B733" t="s">
+        <v>7</v>
+      </c>
+      <c r="C733" t="s">
+        <v>7</v>
+      </c>
+      <c r="D733" t="s">
+        <v>8</v>
+      </c>
+      <c r="E733" t="s">
+        <v>9</v>
+      </c>
+      <c r="F733" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="G733" t="n">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B734" t="s">
+        <v>7</v>
+      </c>
+      <c r="C734" t="s">
+        <v>7</v>
+      </c>
+      <c r="D734" t="s">
+        <v>8</v>
+      </c>
+      <c r="E734" t="s">
+        <v>9</v>
+      </c>
+      <c r="F734" s="1" t="n">
+        <v>45659</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B735" t="s">
+        <v>7</v>
+      </c>
+      <c r="C735" t="s">
+        <v>7</v>
+      </c>
+      <c r="D735" t="s">
+        <v>8</v>
+      </c>
+      <c r="E735" t="s">
+        <v>9</v>
+      </c>
+      <c r="F735" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="G735" t="n">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B736" t="s">
+        <v>7</v>
+      </c>
+      <c r="C736" t="s">
+        <v>7</v>
+      </c>
+      <c r="D736" t="s">
+        <v>8</v>
+      </c>
+      <c r="E736" t="s">
+        <v>9</v>
+      </c>
+      <c r="F736" s="1" t="n">
+        <v>45661</v>
+      </c>
+      <c r="G736" t="n">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B737" t="s">
+        <v>7</v>
+      </c>
+      <c r="C737" t="s">
+        <v>7</v>
+      </c>
+      <c r="D737" t="s">
+        <v>8</v>
+      </c>
+      <c r="E737" t="s">
+        <v>9</v>
+      </c>
+      <c r="F737" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="G737" t="n">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B738" t="s">
+        <v>7</v>
+      </c>
+      <c r="C738" t="s">
+        <v>7</v>
+      </c>
+      <c r="D738" t="s">
+        <v>8</v>
+      </c>
+      <c r="E738" t="s">
+        <v>9</v>
+      </c>
+      <c r="F738" s="1" t="n">
+        <v>45663</v>
+      </c>
+      <c r="G738" t="n">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B739" t="s">
+        <v>7</v>
+      </c>
+      <c r="C739" t="s">
+        <v>7</v>
+      </c>
+      <c r="D739" t="s">
+        <v>8</v>
+      </c>
+      <c r="E739" t="s">
+        <v>9</v>
+      </c>
+      <c r="F739" s="1" t="n">
+        <v>45664</v>
+      </c>
+      <c r="G739" t="n">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B740" t="s">
+        <v>7</v>
+      </c>
+      <c r="C740" t="s">
+        <v>7</v>
+      </c>
+      <c r="D740" t="s">
+        <v>8</v>
+      </c>
+      <c r="E740" t="s">
+        <v>9</v>
+      </c>
+      <c r="F740" s="1" t="n">
+        <v>45665</v>
+      </c>
+      <c r="G740" t="n">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B741" t="s">
+        <v>7</v>
+      </c>
+      <c r="C741" t="s">
+        <v>7</v>
+      </c>
+      <c r="D741" t="s">
+        <v>8</v>
+      </c>
+      <c r="E741" t="s">
+        <v>9</v>
+      </c>
+      <c r="F741" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="G741" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B742" t="s">
+        <v>7</v>
+      </c>
+      <c r="C742" t="s">
+        <v>7</v>
+      </c>
+      <c r="D742" t="s">
+        <v>8</v>
+      </c>
+      <c r="E742" t="s">
+        <v>9</v>
+      </c>
+      <c r="F742" s="1" t="n">
+        <v>45667</v>
+      </c>
+      <c r="G742" t="n">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B743" t="s">
+        <v>7</v>
+      </c>
+      <c r="C743" t="s">
+        <v>7</v>
+      </c>
+      <c r="D743" t="s">
+        <v>8</v>
+      </c>
+      <c r="E743" t="s">
+        <v>9</v>
+      </c>
+      <c r="F743" s="1" t="n">
+        <v>45668</v>
+      </c>
+      <c r="G743" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B744" t="s">
+        <v>7</v>
+      </c>
+      <c r="C744" t="s">
+        <v>7</v>
+      </c>
+      <c r="D744" t="s">
+        <v>8</v>
+      </c>
+      <c r="E744" t="s">
+        <v>9</v>
+      </c>
+      <c r="F744" s="1" t="n">
+        <v>45669</v>
+      </c>
+      <c r="G744" t="n">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B745" t="s">
+        <v>7</v>
+      </c>
+      <c r="C745" t="s">
+        <v>7</v>
+      </c>
+      <c r="D745" t="s">
+        <v>8</v>
+      </c>
+      <c r="E745" t="s">
+        <v>9</v>
+      </c>
+      <c r="F745" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B746" t="s">
+        <v>7</v>
+      </c>
+      <c r="C746" t="s">
+        <v>7</v>
+      </c>
+      <c r="D746" t="s">
+        <v>8</v>
+      </c>
+      <c r="E746" t="s">
+        <v>9</v>
+      </c>
+      <c r="F746" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B747" t="s">
+        <v>7</v>
+      </c>
+      <c r="C747" t="s">
+        <v>7</v>
+      </c>
+      <c r="D747" t="s">
+        <v>8</v>
+      </c>
+      <c r="E747" t="s">
+        <v>9</v>
+      </c>
+      <c r="F747" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="G747" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B748" t="s">
+        <v>7</v>
+      </c>
+      <c r="C748" t="s">
+        <v>7</v>
+      </c>
+      <c r="D748" t="s">
+        <v>8</v>
+      </c>
+      <c r="E748" t="s">
+        <v>9</v>
+      </c>
+      <c r="F748" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="G748" t="n">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B749" t="s">
+        <v>7</v>
+      </c>
+      <c r="C749" t="s">
+        <v>7</v>
+      </c>
+      <c r="D749" t="s">
+        <v>8</v>
+      </c>
+      <c r="E749" t="s">
+        <v>9</v>
+      </c>
+      <c r="F749" s="1" t="n">
+        <v>45674</v>
+      </c>
+      <c r="G749" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B750" t="s">
+        <v>7</v>
+      </c>
+      <c r="C750" t="s">
+        <v>7</v>
+      </c>
+      <c r="D750" t="s">
+        <v>8</v>
+      </c>
+      <c r="E750" t="s">
+        <v>9</v>
+      </c>
+      <c r="F750" s="1" t="n">
+        <v>45675</v>
+      </c>
+      <c r="G750" t="n">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B751" t="s">
+        <v>7</v>
+      </c>
+      <c r="C751" t="s">
+        <v>7</v>
+      </c>
+      <c r="D751" t="s">
+        <v>8</v>
+      </c>
+      <c r="E751" t="s">
+        <v>9</v>
+      </c>
+      <c r="F751" s="1" t="n">
+        <v>45676</v>
+      </c>
+      <c r="G751" t="n">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B752" t="s">
+        <v>7</v>
+      </c>
+      <c r="C752" t="s">
+        <v>7</v>
+      </c>
+      <c r="D752" t="s">
+        <v>8</v>
+      </c>
+      <c r="E752" t="s">
+        <v>9</v>
+      </c>
+      <c r="F752" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="G752" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B753" t="s">
+        <v>7</v>
+      </c>
+      <c r="C753" t="s">
+        <v>7</v>
+      </c>
+      <c r="D753" t="s">
+        <v>8</v>
+      </c>
+      <c r="E753" t="s">
+        <v>9</v>
+      </c>
+      <c r="F753" s="1" t="n">
+        <v>45678</v>
+      </c>
+      <c r="G753" t="n">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B754" t="s">
+        <v>7</v>
+      </c>
+      <c r="C754" t="s">
+        <v>7</v>
+      </c>
+      <c r="D754" t="s">
+        <v>8</v>
+      </c>
+      <c r="E754" t="s">
+        <v>9</v>
+      </c>
+      <c r="F754" s="1" t="n">
+        <v>45679</v>
+      </c>
+      <c r="G754" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B755" t="s">
+        <v>7</v>
+      </c>
+      <c r="C755" t="s">
+        <v>7</v>
+      </c>
+      <c r="D755" t="s">
+        <v>8</v>
+      </c>
+      <c r="E755" t="s">
+        <v>9</v>
+      </c>
+      <c r="F755" s="1" t="n">
+        <v>45680</v>
+      </c>
+      <c r="G755" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B756" t="s">
+        <v>7</v>
+      </c>
+      <c r="C756" t="s">
+        <v>7</v>
+      </c>
+      <c r="D756" t="s">
+        <v>8</v>
+      </c>
+      <c r="E756" t="s">
+        <v>9</v>
+      </c>
+      <c r="F756" s="1" t="n">
+        <v>45681</v>
+      </c>
+      <c r="G756" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B757" t="s">
+        <v>7</v>
+      </c>
+      <c r="C757" t="s">
+        <v>7</v>
+      </c>
+      <c r="D757" t="s">
+        <v>8</v>
+      </c>
+      <c r="E757" t="s">
+        <v>9</v>
+      </c>
+      <c r="F757" s="1" t="n">
+        <v>45682</v>
+      </c>
+      <c r="G757" t="n">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B758" t="s">
+        <v>7</v>
+      </c>
+      <c r="C758" t="s">
+        <v>7</v>
+      </c>
+      <c r="D758" t="s">
+        <v>8</v>
+      </c>
+      <c r="E758" t="s">
+        <v>9</v>
+      </c>
+      <c r="F758" s="1" t="n">
+        <v>45683</v>
+      </c>
+      <c r="G758" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B759" t="s">
+        <v>7</v>
+      </c>
+      <c r="C759" t="s">
+        <v>7</v>
+      </c>
+      <c r="D759" t="s">
+        <v>8</v>
+      </c>
+      <c r="E759" t="s">
+        <v>9</v>
+      </c>
+      <c r="F759" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B760" t="s">
+        <v>7</v>
+      </c>
+      <c r="C760" t="s">
+        <v>7</v>
+      </c>
+      <c r="D760" t="s">
+        <v>8</v>
+      </c>
+      <c r="E760" t="s">
+        <v>9</v>
+      </c>
+      <c r="F760" s="1" t="n">
+        <v>45685</v>
+      </c>
+      <c r="G760" t="n">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B761" t="s">
+        <v>7</v>
+      </c>
+      <c r="C761" t="s">
+        <v>7</v>
+      </c>
+      <c r="D761" t="s">
+        <v>8</v>
+      </c>
+      <c r="E761" t="s">
+        <v>9</v>
+      </c>
+      <c r="F761" s="1" t="n">
+        <v>45686</v>
+      </c>
+      <c r="G761" t="n">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B762" t="s">
+        <v>7</v>
+      </c>
+      <c r="C762" t="s">
+        <v>7</v>
+      </c>
+      <c r="D762" t="s">
+        <v>8</v>
+      </c>
+      <c r="E762" t="s">
+        <v>9</v>
+      </c>
+      <c r="F762" s="1" t="n">
+        <v>45687</v>
+      </c>
+      <c r="G762" t="n">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B763" t="s">
+        <v>7</v>
+      </c>
+      <c r="C763" t="s">
+        <v>7</v>
+      </c>
+      <c r="D763" t="s">
+        <v>8</v>
+      </c>
+      <c r="E763" t="s">
+        <v>9</v>
+      </c>
+      <c r="F763" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="G763" t="n">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B764" t="s">
+        <v>7</v>
+      </c>
+      <c r="C764" t="s">
+        <v>7</v>
+      </c>
+      <c r="D764" t="s">
+        <v>8</v>
+      </c>
+      <c r="E764" t="s">
+        <v>9</v>
+      </c>
+      <c r="F764" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="G764" t="n">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B765" t="s">
+        <v>7</v>
+      </c>
+      <c r="C765" t="s">
+        <v>7</v>
+      </c>
+      <c r="D765" t="s">
+        <v>8</v>
+      </c>
+      <c r="E765" t="s">
+        <v>9</v>
+      </c>
+      <c r="F765" s="1" t="n">
+        <v>45690</v>
+      </c>
+      <c r="G765" t="n">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B766" t="s">
+        <v>7</v>
+      </c>
+      <c r="C766" t="s">
+        <v>7</v>
+      </c>
+      <c r="D766" t="s">
+        <v>8</v>
+      </c>
+      <c r="E766" t="s">
+        <v>9</v>
+      </c>
+      <c r="F766" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="G766" t="n">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B767" t="s">
+        <v>7</v>
+      </c>
+      <c r="C767" t="s">
+        <v>7</v>
+      </c>
+      <c r="D767" t="s">
+        <v>8</v>
+      </c>
+      <c r="E767" t="s">
+        <v>9</v>
+      </c>
+      <c r="F767" s="1" t="n">
+        <v>45692</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B768" t="s">
+        <v>7</v>
+      </c>
+      <c r="C768" t="s">
+        <v>7</v>
+      </c>
+      <c r="D768" t="s">
+        <v>8</v>
+      </c>
+      <c r="E768" t="s">
+        <v>9</v>
+      </c>
+      <c r="F768" s="1" t="n">
+        <v>45693</v>
+      </c>
+      <c r="G768" t="n">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B769" t="s">
+        <v>7</v>
+      </c>
+      <c r="C769" t="s">
+        <v>7</v>
+      </c>
+      <c r="D769" t="s">
+        <v>8</v>
+      </c>
+      <c r="E769" t="s">
+        <v>9</v>
+      </c>
+      <c r="F769" s="1" t="n">
+        <v>45694</v>
+      </c>
+      <c r="G769" t="n">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B770" t="s">
+        <v>7</v>
+      </c>
+      <c r="C770" t="s">
+        <v>7</v>
+      </c>
+      <c r="D770" t="s">
+        <v>8</v>
+      </c>
+      <c r="E770" t="s">
+        <v>9</v>
+      </c>
+      <c r="F770" s="1" t="n">
+        <v>45695</v>
+      </c>
+      <c r="G770" t="n">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B771" t="s">
+        <v>7</v>
+      </c>
+      <c r="C771" t="s">
+        <v>7</v>
+      </c>
+      <c r="D771" t="s">
+        <v>8</v>
+      </c>
+      <c r="E771" t="s">
+        <v>9</v>
+      </c>
+      <c r="F771" s="1" t="n">
+        <v>45696</v>
+      </c>
+      <c r="G771" t="n">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B772" t="s">
+        <v>7</v>
+      </c>
+      <c r="C772" t="s">
+        <v>7</v>
+      </c>
+      <c r="D772" t="s">
+        <v>8</v>
+      </c>
+      <c r="E772" t="s">
+        <v>9</v>
+      </c>
+      <c r="F772" s="1" t="n">
+        <v>45697</v>
+      </c>
+      <c r="G772" t="n">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B773" t="s">
+        <v>7</v>
+      </c>
+      <c r="C773" t="s">
+        <v>7</v>
+      </c>
+      <c r="D773" t="s">
+        <v>8</v>
+      </c>
+      <c r="E773" t="s">
+        <v>9</v>
+      </c>
+      <c r="F773" s="1" t="n">
+        <v>45698</v>
+      </c>
+      <c r="G773" t="n">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B774" t="s">
+        <v>7</v>
+      </c>
+      <c r="C774" t="s">
+        <v>7</v>
+      </c>
+      <c r="D774" t="s">
+        <v>8</v>
+      </c>
+      <c r="E774" t="s">
+        <v>9</v>
+      </c>
+      <c r="F774" s="1" t="n">
+        <v>45699</v>
+      </c>
+      <c r="G774" t="n">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B775" t="s">
+        <v>7</v>
+      </c>
+      <c r="C775" t="s">
+        <v>7</v>
+      </c>
+      <c r="D775" t="s">
+        <v>8</v>
+      </c>
+      <c r="E775" t="s">
+        <v>9</v>
+      </c>
+      <c r="F775" s="1" t="n">
+        <v>45700</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B776" t="s">
+        <v>7</v>
+      </c>
+      <c r="C776" t="s">
+        <v>7</v>
+      </c>
+      <c r="D776" t="s">
+        <v>8</v>
+      </c>
+      <c r="E776" t="s">
+        <v>9</v>
+      </c>
+      <c r="F776" s="1" t="n">
+        <v>45701</v>
+      </c>
+      <c r="G776" t="n">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B777" t="s">
+        <v>7</v>
+      </c>
+      <c r="C777" t="s">
+        <v>7</v>
+      </c>
+      <c r="D777" t="s">
+        <v>8</v>
+      </c>
+      <c r="E777" t="s">
+        <v>9</v>
+      </c>
+      <c r="F777" s="1" t="n">
+        <v>45702</v>
+      </c>
+      <c r="G777" t="n">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B778" t="s">
+        <v>7</v>
+      </c>
+      <c r="C778" t="s">
+        <v>7</v>
+      </c>
+      <c r="D778" t="s">
+        <v>8</v>
+      </c>
+      <c r="E778" t="s">
+        <v>9</v>
+      </c>
+      <c r="F778" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="G778" t="n">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B779" t="s">
+        <v>7</v>
+      </c>
+      <c r="C779" t="s">
+        <v>7</v>
+      </c>
+      <c r="D779" t="s">
+        <v>8</v>
+      </c>
+      <c r="E779" t="s">
+        <v>9</v>
+      </c>
+      <c r="F779" s="1" t="n">
+        <v>45704</v>
+      </c>
+      <c r="G779" t="n">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B780" t="s">
+        <v>7</v>
+      </c>
+      <c r="C780" t="s">
+        <v>7</v>
+      </c>
+      <c r="D780" t="s">
+        <v>8</v>
+      </c>
+      <c r="E780" t="s">
+        <v>9</v>
+      </c>
+      <c r="F780" s="1" t="n">
+        <v>45705</v>
+      </c>
+      <c r="G780" t="n">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B781" t="s">
+        <v>7</v>
+      </c>
+      <c r="C781" t="s">
+        <v>7</v>
+      </c>
+      <c r="D781" t="s">
+        <v>8</v>
+      </c>
+      <c r="E781" t="s">
+        <v>9</v>
+      </c>
+      <c r="F781" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="G781" t="n">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B782" t="s">
+        <v>7</v>
+      </c>
+      <c r="C782" t="s">
+        <v>7</v>
+      </c>
+      <c r="D782" t="s">
+        <v>8</v>
+      </c>
+      <c r="E782" t="s">
+        <v>9</v>
+      </c>
+      <c r="F782" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="G782" t="n">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B783" t="s">
+        <v>7</v>
+      </c>
+      <c r="C783" t="s">
+        <v>7</v>
+      </c>
+      <c r="D783" t="s">
+        <v>8</v>
+      </c>
+      <c r="E783" t="s">
+        <v>9</v>
+      </c>
+      <c r="F783" s="1" t="n">
+        <v>45708</v>
+      </c>
+      <c r="G783" t="n">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B784" t="s">
+        <v>7</v>
+      </c>
+      <c r="C784" t="s">
+        <v>7</v>
+      </c>
+      <c r="D784" t="s">
+        <v>8</v>
+      </c>
+      <c r="E784" t="s">
+        <v>9</v>
+      </c>
+      <c r="F784" s="1" t="n">
+        <v>45709</v>
+      </c>
+      <c r="G784" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B785" t="s">
+        <v>7</v>
+      </c>
+      <c r="C785" t="s">
+        <v>7</v>
+      </c>
+      <c r="D785" t="s">
+        <v>8</v>
+      </c>
+      <c r="E785" t="s">
+        <v>9</v>
+      </c>
+      <c r="F785" s="1" t="n">
+        <v>45710</v>
+      </c>
+      <c r="G785" t="n">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B786" t="s">
+        <v>7</v>
+      </c>
+      <c r="C786" t="s">
+        <v>7</v>
+      </c>
+      <c r="D786" t="s">
+        <v>8</v>
+      </c>
+      <c r="E786" t="s">
+        <v>9</v>
+      </c>
+      <c r="F786" s="1" t="n">
+        <v>45711</v>
+      </c>
+      <c r="G786" t="n">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B787" t="s">
+        <v>7</v>
+      </c>
+      <c r="C787" t="s">
+        <v>7</v>
+      </c>
+      <c r="D787" t="s">
+        <v>8</v>
+      </c>
+      <c r="E787" t="s">
+        <v>9</v>
+      </c>
+      <c r="F787" s="1" t="n">
+        <v>45712</v>
+      </c>
+      <c r="G787" t="n">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B788" t="s">
+        <v>7</v>
+      </c>
+      <c r="C788" t="s">
+        <v>7</v>
+      </c>
+      <c r="D788" t="s">
+        <v>8</v>
+      </c>
+      <c r="E788" t="s">
+        <v>9</v>
+      </c>
+      <c r="F788" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="G788" t="n">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B789" t="s">
+        <v>7</v>
+      </c>
+      <c r="C789" t="s">
+        <v>7</v>
+      </c>
+      <c r="D789" t="s">
+        <v>8</v>
+      </c>
+      <c r="E789" t="s">
+        <v>9</v>
+      </c>
+      <c r="F789" s="1" t="n">
+        <v>45714</v>
+      </c>
+      <c r="G789" t="n">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B790" t="s">
+        <v>7</v>
+      </c>
+      <c r="C790" t="s">
+        <v>7</v>
+      </c>
+      <c r="D790" t="s">
+        <v>8</v>
+      </c>
+      <c r="E790" t="s">
+        <v>9</v>
+      </c>
+      <c r="F790" s="1" t="n">
+        <v>45715</v>
+      </c>
+      <c r="G790" t="n">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B791" t="s">
+        <v>7</v>
+      </c>
+      <c r="C791" t="s">
+        <v>7</v>
+      </c>
+      <c r="D791" t="s">
+        <v>8</v>
+      </c>
+      <c r="E791" t="s">
+        <v>9</v>
+      </c>
+      <c r="F791" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="G791" t="n">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B792" t="s">
+        <v>7</v>
+      </c>
+      <c r="C792" t="s">
+        <v>7</v>
+      </c>
+      <c r="D792" t="s">
+        <v>8</v>
+      </c>
+      <c r="E792" t="s">
+        <v>9</v>
+      </c>
+      <c r="F792" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="G792" t="n">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B793" t="s">
+        <v>7</v>
+      </c>
+      <c r="C793" t="s">
+        <v>7</v>
+      </c>
+      <c r="D793" t="s">
+        <v>8</v>
+      </c>
+      <c r="E793" t="s">
+        <v>9</v>
+      </c>
+      <c r="F793" s="1" t="n">
+        <v>45718</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B794" t="s">
+        <v>7</v>
+      </c>
+      <c r="C794" t="s">
+        <v>7</v>
+      </c>
+      <c r="D794" t="s">
+        <v>8</v>
+      </c>
+      <c r="E794" t="s">
+        <v>9</v>
+      </c>
+      <c r="F794" s="1" t="n">
+        <v>45719</v>
+      </c>
+      <c r="G794" t="n">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B795" t="s">
+        <v>7</v>
+      </c>
+      <c r="C795" t="s">
+        <v>7</v>
+      </c>
+      <c r="D795" t="s">
+        <v>8</v>
+      </c>
+      <c r="E795" t="s">
+        <v>9</v>
+      </c>
+      <c r="F795" s="1" t="n">
+        <v>45720</v>
+      </c>
+      <c r="G795" t="n">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B796" t="s">
+        <v>7</v>
+      </c>
+      <c r="C796" t="s">
+        <v>7</v>
+      </c>
+      <c r="D796" t="s">
+        <v>8</v>
+      </c>
+      <c r="E796" t="s">
+        <v>9</v>
+      </c>
+      <c r="F796" s="1" t="n">
+        <v>45721</v>
+      </c>
+      <c r="G796" t="n">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B797" t="s">
+        <v>7</v>
+      </c>
+      <c r="C797" t="s">
+        <v>7</v>
+      </c>
+      <c r="D797" t="s">
+        <v>8</v>
+      </c>
+      <c r="E797" t="s">
+        <v>9</v>
+      </c>
+      <c r="F797" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="G797" t="n">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B798" t="s">
+        <v>7</v>
+      </c>
+      <c r="C798" t="s">
+        <v>7</v>
+      </c>
+      <c r="D798" t="s">
+        <v>8</v>
+      </c>
+      <c r="E798" t="s">
+        <v>9</v>
+      </c>
+      <c r="F798" s="1" t="n">
+        <v>45723</v>
+      </c>
+      <c r="G798" t="n">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B799" t="s">
+        <v>7</v>
+      </c>
+      <c r="C799" t="s">
+        <v>7</v>
+      </c>
+      <c r="D799" t="s">
+        <v>8</v>
+      </c>
+      <c r="E799" t="s">
+        <v>9</v>
+      </c>
+      <c r="F799" s="1" t="n">
+        <v>45724</v>
+      </c>
+      <c r="G799" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B800" t="s">
+        <v>7</v>
+      </c>
+      <c r="C800" t="s">
+        <v>7</v>
+      </c>
+      <c r="D800" t="s">
+        <v>8</v>
+      </c>
+      <c r="E800" t="s">
+        <v>9</v>
+      </c>
+      <c r="F800" s="1" t="n">
+        <v>45725</v>
+      </c>
+      <c r="G800" t="n">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B801" t="s">
+        <v>7</v>
+      </c>
+      <c r="C801" t="s">
+        <v>7</v>
+      </c>
+      <c r="D801" t="s">
+        <v>8</v>
+      </c>
+      <c r="E801" t="s">
+        <v>9</v>
+      </c>
+      <c r="F801" s="1" t="n">
+        <v>45726</v>
+      </c>
+      <c r="G801" t="n">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B802" t="s">
+        <v>7</v>
+      </c>
+      <c r="C802" t="s">
+        <v>7</v>
+      </c>
+      <c r="D802" t="s">
+        <v>8</v>
+      </c>
+      <c r="E802" t="s">
+        <v>9</v>
+      </c>
+      <c r="F802" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B803" t="s">
+        <v>7</v>
+      </c>
+      <c r="C803" t="s">
+        <v>7</v>
+      </c>
+      <c r="D803" t="s">
+        <v>8</v>
+      </c>
+      <c r="E803" t="s">
+        <v>9</v>
+      </c>
+      <c r="F803" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="G803" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B804" t="s">
+        <v>7</v>
+      </c>
+      <c r="C804" t="s">
+        <v>7</v>
+      </c>
+      <c r="D804" t="s">
+        <v>8</v>
+      </c>
+      <c r="E804" t="s">
+        <v>9</v>
+      </c>
+      <c r="F804" s="1" t="n">
+        <v>45729</v>
+      </c>
+      <c r="G804" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B805" t="s">
+        <v>7</v>
+      </c>
+      <c r="C805" t="s">
+        <v>7</v>
+      </c>
+      <c r="D805" t="s">
+        <v>8</v>
+      </c>
+      <c r="E805" t="s">
+        <v>9</v>
+      </c>
+      <c r="F805" s="1" t="n">
+        <v>45730</v>
+      </c>
+      <c r="G805" t="n">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B806" t="s">
+        <v>7</v>
+      </c>
+      <c r="C806" t="s">
+        <v>7</v>
+      </c>
+      <c r="D806" t="s">
+        <v>8</v>
+      </c>
+      <c r="E806" t="s">
+        <v>9</v>
+      </c>
+      <c r="F806" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="G806" t="n">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B807" t="s">
+        <v>7</v>
+      </c>
+      <c r="C807" t="s">
+        <v>7</v>
+      </c>
+      <c r="D807" t="s">
+        <v>8</v>
+      </c>
+      <c r="E807" t="s">
+        <v>9</v>
+      </c>
+      <c r="F807" s="1" t="n">
+        <v>45732</v>
+      </c>
+      <c r="G807" t="n">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B808" t="s">
+        <v>7</v>
+      </c>
+      <c r="C808" t="s">
+        <v>7</v>
+      </c>
+      <c r="D808" t="s">
+        <v>8</v>
+      </c>
+      <c r="E808" t="s">
+        <v>9</v>
+      </c>
+      <c r="F808" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="G808" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B809" t="s">
+        <v>7</v>
+      </c>
+      <c r="C809" t="s">
+        <v>7</v>
+      </c>
+      <c r="D809" t="s">
+        <v>8</v>
+      </c>
+      <c r="E809" t="s">
+        <v>9</v>
+      </c>
+      <c r="F809" s="1" t="n">
+        <v>45734</v>
+      </c>
+      <c r="G809" t="n">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B810" t="s">
+        <v>7</v>
+      </c>
+      <c r="C810" t="s">
+        <v>7</v>
+      </c>
+      <c r="D810" t="s">
+        <v>8</v>
+      </c>
+      <c r="E810" t="s">
+        <v>9</v>
+      </c>
+      <c r="F810" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="G810" t="n">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B811" t="s">
+        <v>7</v>
+      </c>
+      <c r="C811" t="s">
+        <v>7</v>
+      </c>
+      <c r="D811" t="s">
+        <v>8</v>
+      </c>
+      <c r="E811" t="s">
+        <v>9</v>
+      </c>
+      <c r="F811" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="G811" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B812" t="s">
+        <v>7</v>
+      </c>
+      <c r="C812" t="s">
+        <v>7</v>
+      </c>
+      <c r="D812" t="s">
+        <v>8</v>
+      </c>
+      <c r="E812" t="s">
+        <v>9</v>
+      </c>
+      <c r="F812" s="1" t="n">
+        <v>45737</v>
+      </c>
+      <c r="G812" t="n">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B813" t="s">
+        <v>7</v>
+      </c>
+      <c r="C813" t="s">
+        <v>7</v>
+      </c>
+      <c r="D813" t="s">
+        <v>8</v>
+      </c>
+      <c r="E813" t="s">
+        <v>9</v>
+      </c>
+      <c r="F813" s="1" t="n">
+        <v>45738</v>
+      </c>
+      <c r="G813" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B814" t="s">
+        <v>7</v>
+      </c>
+      <c r="C814" t="s">
+        <v>7</v>
+      </c>
+      <c r="D814" t="s">
+        <v>8</v>
+      </c>
+      <c r="E814" t="s">
+        <v>9</v>
+      </c>
+      <c r="F814" s="1" t="n">
+        <v>45739</v>
+      </c>
+      <c r="G814" t="n">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B815" t="s">
+        <v>7</v>
+      </c>
+      <c r="C815" t="s">
+        <v>7</v>
+      </c>
+      <c r="D815" t="s">
+        <v>8</v>
+      </c>
+      <c r="E815" t="s">
+        <v>9</v>
+      </c>
+      <c r="F815" s="1" t="n">
+        <v>45740</v>
+      </c>
+      <c r="G815" t="n">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B816" t="s">
+        <v>7</v>
+      </c>
+      <c r="C816" t="s">
+        <v>7</v>
+      </c>
+      <c r="D816" t="s">
+        <v>8</v>
+      </c>
+      <c r="E816" t="s">
+        <v>9</v>
+      </c>
+      <c r="F816" s="1" t="n">
+        <v>45741</v>
+      </c>
+      <c r="G816" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B817" t="s">
+        <v>7</v>
+      </c>
+      <c r="C817" t="s">
+        <v>7</v>
+      </c>
+      <c r="D817" t="s">
+        <v>8</v>
+      </c>
+      <c r="E817" t="s">
+        <v>9</v>
+      </c>
+      <c r="F817" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="G817" t="n">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B818" t="s">
+        <v>7</v>
+      </c>
+      <c r="C818" t="s">
+        <v>7</v>
+      </c>
+      <c r="D818" t="s">
+        <v>8</v>
+      </c>
+      <c r="E818" t="s">
+        <v>9</v>
+      </c>
+      <c r="F818" s="1" t="n">
+        <v>45743</v>
+      </c>
+      <c r="G818" t="n">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B819" t="s">
+        <v>7</v>
+      </c>
+      <c r="C819" t="s">
+        <v>7</v>
+      </c>
+      <c r="D819" t="s">
+        <v>8</v>
+      </c>
+      <c r="E819" t="s">
+        <v>9</v>
+      </c>
+      <c r="F819" s="1" t="n">
+        <v>45744</v>
+      </c>
+      <c r="G819" t="n">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B820" t="s">
+        <v>7</v>
+      </c>
+      <c r="C820" t="s">
+        <v>7</v>
+      </c>
+      <c r="D820" t="s">
+        <v>8</v>
+      </c>
+      <c r="E820" t="s">
+        <v>9</v>
+      </c>
+      <c r="F820" s="1" t="n">
+        <v>45745</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B821" t="s">
+        <v>7</v>
+      </c>
+      <c r="C821" t="s">
+        <v>7</v>
+      </c>
+      <c r="D821" t="s">
+        <v>8</v>
+      </c>
+      <c r="E821" t="s">
+        <v>9</v>
+      </c>
+      <c r="F821" s="1" t="n">
+        <v>45746</v>
+      </c>
+      <c r="G821" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B822" t="s">
+        <v>7</v>
+      </c>
+      <c r="C822" t="s">
+        <v>7</v>
+      </c>
+      <c r="D822" t="s">
+        <v>8</v>
+      </c>
+      <c r="E822" t="s">
+        <v>9</v>
+      </c>
+      <c r="F822" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="G822" t="n">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B823" t="s">
+        <v>7</v>
+      </c>
+      <c r="C823" t="s">
+        <v>7</v>
+      </c>
+      <c r="D823" t="s">
+        <v>8</v>
+      </c>
+      <c r="E823" t="s">
+        <v>9</v>
+      </c>
+      <c r="F823" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="G823" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B824" t="s">
+        <v>7</v>
+      </c>
+      <c r="C824" t="s">
+        <v>7</v>
+      </c>
+      <c r="D824" t="s">
+        <v>8</v>
+      </c>
+      <c r="E824" t="s">
+        <v>9</v>
+      </c>
+      <c r="F824" s="1" t="n">
+        <v>45749</v>
+      </c>
+      <c r="G824" t="n">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B825" t="s">
+        <v>7</v>
+      </c>
+      <c r="C825" t="s">
+        <v>7</v>
+      </c>
+      <c r="D825" t="s">
+        <v>8</v>
+      </c>
+      <c r="E825" t="s">
+        <v>9</v>
+      </c>
+      <c r="F825" s="1" t="n">
+        <v>45750</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B826" t="s">
+        <v>7</v>
+      </c>
+      <c r="C826" t="s">
+        <v>7</v>
+      </c>
+      <c r="D826" t="s">
+        <v>8</v>
+      </c>
+      <c r="E826" t="s">
+        <v>9</v>
+      </c>
+      <c r="F826" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="G826" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B827" t="s">
+        <v>7</v>
+      </c>
+      <c r="C827" t="s">
+        <v>7</v>
+      </c>
+      <c r="D827" t="s">
+        <v>8</v>
+      </c>
+      <c r="E827" t="s">
+        <v>9</v>
+      </c>
+      <c r="F827" s="1" t="n">
+        <v>45752</v>
+      </c>
+      <c r="G827" t="n">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B828" t="s">
+        <v>7</v>
+      </c>
+      <c r="C828" t="s">
+        <v>7</v>
+      </c>
+      <c r="D828" t="s">
+        <v>8</v>
+      </c>
+      <c r="E828" t="s">
+        <v>9</v>
+      </c>
+      <c r="F828" s="1" t="n">
+        <v>45753</v>
+      </c>
+      <c r="G828" t="n">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B829" t="s">
+        <v>7</v>
+      </c>
+      <c r="C829" t="s">
+        <v>7</v>
+      </c>
+      <c r="D829" t="s">
+        <v>8</v>
+      </c>
+      <c r="E829" t="s">
+        <v>9</v>
+      </c>
+      <c r="F829" s="1" t="n">
+        <v>45754</v>
+      </c>
+      <c r="G829" t="n">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B830" t="s">
+        <v>7</v>
+      </c>
+      <c r="C830" t="s">
+        <v>7</v>
+      </c>
+      <c r="D830" t="s">
+        <v>8</v>
+      </c>
+      <c r="E830" t="s">
+        <v>9</v>
+      </c>
+      <c r="F830" s="1" t="n">
+        <v>45755</v>
+      </c>
+      <c r="G830" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B831" t="s">
+        <v>7</v>
+      </c>
+      <c r="C831" t="s">
+        <v>7</v>
+      </c>
+      <c r="D831" t="s">
+        <v>8</v>
+      </c>
+      <c r="E831" t="s">
+        <v>9</v>
+      </c>
+      <c r="F831" s="1" t="n">
+        <v>45756</v>
+      </c>
+      <c r="G831" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B832" t="s">
+        <v>7</v>
+      </c>
+      <c r="C832" t="s">
+        <v>7</v>
+      </c>
+      <c r="D832" t="s">
+        <v>8</v>
+      </c>
+      <c r="E832" t="s">
+        <v>9</v>
+      </c>
+      <c r="F832" s="1" t="n">
+        <v>45757</v>
+      </c>
+      <c r="G832" t="n">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B833" t="s">
+        <v>7</v>
+      </c>
+      <c r="C833" t="s">
+        <v>7</v>
+      </c>
+      <c r="D833" t="s">
+        <v>8</v>
+      </c>
+      <c r="E833" t="s">
+        <v>9</v>
+      </c>
+      <c r="F833" s="1" t="n">
+        <v>45758</v>
+      </c>
+      <c r="G833" t="n">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B834" t="s">
+        <v>7</v>
+      </c>
+      <c r="C834" t="s">
+        <v>7</v>
+      </c>
+      <c r="D834" t="s">
+        <v>8</v>
+      </c>
+      <c r="E834" t="s">
+        <v>9</v>
+      </c>
+      <c r="F834" s="1" t="n">
+        <v>45759</v>
+      </c>
+      <c r="G834" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B835" t="s">
+        <v>7</v>
+      </c>
+      <c r="C835" t="s">
+        <v>7</v>
+      </c>
+      <c r="D835" t="s">
+        <v>8</v>
+      </c>
+      <c r="E835" t="s">
+        <v>9</v>
+      </c>
+      <c r="F835" s="1" t="n">
+        <v>45760</v>
+      </c>
+      <c r="G835" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B836" t="s">
+        <v>7</v>
+      </c>
+      <c r="C836" t="s">
+        <v>7</v>
+      </c>
+      <c r="D836" t="s">
+        <v>8</v>
+      </c>
+      <c r="E836" t="s">
+        <v>9</v>
+      </c>
+      <c r="F836" s="1" t="n">
+        <v>45761</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B837" t="s">
+        <v>7</v>
+      </c>
+      <c r="C837" t="s">
+        <v>7</v>
+      </c>
+      <c r="D837" t="s">
+        <v>8</v>
+      </c>
+      <c r="E837" t="s">
+        <v>9</v>
+      </c>
+      <c r="F837" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B838" t="s">
+        <v>7</v>
+      </c>
+      <c r="C838" t="s">
+        <v>7</v>
+      </c>
+      <c r="D838" t="s">
+        <v>8</v>
+      </c>
+      <c r="E838" t="s">
+        <v>9</v>
+      </c>
+      <c r="F838" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="G838" t="n">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B839" t="s">
+        <v>7</v>
+      </c>
+      <c r="C839" t="s">
+        <v>7</v>
+      </c>
+      <c r="D839" t="s">
+        <v>8</v>
+      </c>
+      <c r="E839" t="s">
+        <v>9</v>
+      </c>
+      <c r="F839" s="1" t="n">
+        <v>45764</v>
+      </c>
+      <c r="G839" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B840" t="s">
+        <v>7</v>
+      </c>
+      <c r="C840" t="s">
+        <v>7</v>
+      </c>
+      <c r="D840" t="s">
+        <v>8</v>
+      </c>
+      <c r="E840" t="s">
+        <v>9</v>
+      </c>
+      <c r="F840" s="1" t="n">
+        <v>45765</v>
+      </c>
+      <c r="G840" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B841" t="s">
+        <v>7</v>
+      </c>
+      <c r="C841" t="s">
+        <v>7</v>
+      </c>
+      <c r="D841" t="s">
+        <v>8</v>
+      </c>
+      <c r="E841" t="s">
+        <v>9</v>
+      </c>
+      <c r="F841" s="1" t="n">
+        <v>45766</v>
+      </c>
+      <c r="G841" t="n">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B842" t="s">
+        <v>7</v>
+      </c>
+      <c r="C842" t="s">
+        <v>7</v>
+      </c>
+      <c r="D842" t="s">
+        <v>8</v>
+      </c>
+      <c r="E842" t="s">
+        <v>9</v>
+      </c>
+      <c r="F842" s="1" t="n">
+        <v>45767</v>
+      </c>
+      <c r="G842" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B843" t="s">
+        <v>7</v>
+      </c>
+      <c r="C843" t="s">
+        <v>7</v>
+      </c>
+      <c r="D843" t="s">
+        <v>8</v>
+      </c>
+      <c r="E843" t="s">
+        <v>9</v>
+      </c>
+      <c r="F843" s="1" t="n">
+        <v>45768</v>
+      </c>
+      <c r="G843" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B844" t="s">
+        <v>7</v>
+      </c>
+      <c r="C844" t="s">
+        <v>7</v>
+      </c>
+      <c r="D844" t="s">
+        <v>8</v>
+      </c>
+      <c r="E844" t="s">
+        <v>9</v>
+      </c>
+      <c r="F844" s="1" t="n">
+        <v>45769</v>
+      </c>
+      <c r="G844" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B845" t="s">
+        <v>7</v>
+      </c>
+      <c r="C845" t="s">
+        <v>7</v>
+      </c>
+      <c r="D845" t="s">
+        <v>8</v>
+      </c>
+      <c r="E845" t="s">
+        <v>9</v>
+      </c>
+      <c r="F845" s="1" t="n">
+        <v>45770</v>
+      </c>
+      <c r="G845" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B846" t="s">
+        <v>7</v>
+      </c>
+      <c r="C846" t="s">
+        <v>7</v>
+      </c>
+      <c r="D846" t="s">
+        <v>8</v>
+      </c>
+      <c r="E846" t="s">
+        <v>9</v>
+      </c>
+      <c r="F846" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="G846" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B847" t="s">
+        <v>7</v>
+      </c>
+      <c r="C847" t="s">
+        <v>7</v>
+      </c>
+      <c r="D847" t="s">
+        <v>8</v>
+      </c>
+      <c r="E847" t="s">
+        <v>9</v>
+      </c>
+      <c r="F847" s="1" t="n">
+        <v>45772</v>
+      </c>
+      <c r="G847" t="n">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B848" t="s">
+        <v>7</v>
+      </c>
+      <c r="C848" t="s">
+        <v>7</v>
+      </c>
+      <c r="D848" t="s">
+        <v>8</v>
+      </c>
+      <c r="E848" t="s">
+        <v>9</v>
+      </c>
+      <c r="F848" s="1" t="n">
+        <v>45773</v>
+      </c>
+      <c r="G848" t="n">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B849" t="s">
+        <v>7</v>
+      </c>
+      <c r="C849" t="s">
+        <v>7</v>
+      </c>
+      <c r="D849" t="s">
+        <v>8</v>
+      </c>
+      <c r="E849" t="s">
+        <v>9</v>
+      </c>
+      <c r="F849" s="1" t="n">
+        <v>45774</v>
+      </c>
+      <c r="G849" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B850" t="s">
+        <v>7</v>
+      </c>
+      <c r="C850" t="s">
+        <v>7</v>
+      </c>
+      <c r="D850" t="s">
+        <v>8</v>
+      </c>
+      <c r="E850" t="s">
+        <v>9</v>
+      </c>
+      <c r="F850" s="1" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G850" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B851" t="s">
+        <v>7</v>
+      </c>
+      <c r="C851" t="s">
+        <v>7</v>
+      </c>
+      <c r="D851" t="s">
+        <v>8</v>
+      </c>
+      <c r="E851" t="s">
+        <v>9</v>
+      </c>
+      <c r="F851" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="G851" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B852" t="s">
+        <v>7</v>
+      </c>
+      <c r="C852" t="s">
+        <v>7</v>
+      </c>
+      <c r="D852" t="s">
+        <v>8</v>
+      </c>
+      <c r="E852" t="s">
+        <v>9</v>
+      </c>
+      <c r="F852" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="G852" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B853" t="s">
+        <v>7</v>
+      </c>
+      <c r="C853" t="s">
+        <v>7</v>
+      </c>
+      <c r="D853" t="s">
+        <v>8</v>
+      </c>
+      <c r="E853" t="s">
+        <v>9</v>
+      </c>
+      <c r="F853" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="G853" t="n">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B854" t="s">
+        <v>7</v>
+      </c>
+      <c r="C854" t="s">
+        <v>7</v>
+      </c>
+      <c r="D854" t="s">
+        <v>8</v>
+      </c>
+      <c r="E854" t="s">
+        <v>9</v>
+      </c>
+      <c r="F854" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="G854" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B855" t="s">
+        <v>7</v>
+      </c>
+      <c r="C855" t="s">
+        <v>7</v>
+      </c>
+      <c r="D855" t="s">
+        <v>8</v>
+      </c>
+      <c r="E855" t="s">
+        <v>9</v>
+      </c>
+      <c r="F855" s="1" t="n">
+        <v>45780</v>
+      </c>
+      <c r="G855" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B856" t="s">
+        <v>7</v>
+      </c>
+      <c r="C856" t="s">
+        <v>7</v>
+      </c>
+      <c r="D856" t="s">
+        <v>8</v>
+      </c>
+      <c r="E856" t="s">
+        <v>9</v>
+      </c>
+      <c r="F856" s="1" t="n">
+        <v>45781</v>
+      </c>
+      <c r="G856" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B857" t="s">
+        <v>7</v>
+      </c>
+      <c r="C857" t="s">
+        <v>7</v>
+      </c>
+      <c r="D857" t="s">
+        <v>8</v>
+      </c>
+      <c r="E857" t="s">
+        <v>9</v>
+      </c>
+      <c r="F857" s="1" t="n">
+        <v>45782</v>
+      </c>
+      <c r="G857" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B858" t="s">
+        <v>7</v>
+      </c>
+      <c r="C858" t="s">
+        <v>7</v>
+      </c>
+      <c r="D858" t="s">
+        <v>8</v>
+      </c>
+      <c r="E858" t="s">
+        <v>9</v>
+      </c>
+      <c r="F858" s="1" t="n">
+        <v>45783</v>
+      </c>
+      <c r="G858" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B859" t="s">
+        <v>7</v>
+      </c>
+      <c r="C859" t="s">
+        <v>7</v>
+      </c>
+      <c r="D859" t="s">
+        <v>8</v>
+      </c>
+      <c r="E859" t="s">
+        <v>9</v>
+      </c>
+      <c r="F859" s="1" t="n">
+        <v>45784</v>
+      </c>
+      <c r="G859" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B860" t="s">
+        <v>7</v>
+      </c>
+      <c r="C860" t="s">
+        <v>7</v>
+      </c>
+      <c r="D860" t="s">
+        <v>8</v>
+      </c>
+      <c r="E860" t="s">
+        <v>9</v>
+      </c>
+      <c r="F860" s="1" t="n">
+        <v>45785</v>
+      </c>
+      <c r="G860" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B861" t="s">
+        <v>7</v>
+      </c>
+      <c r="C861" t="s">
+        <v>7</v>
+      </c>
+      <c r="D861" t="s">
+        <v>8</v>
+      </c>
+      <c r="E861" t="s">
+        <v>9</v>
+      </c>
+      <c r="F861" s="1" t="n">
+        <v>45786</v>
+      </c>
+      <c r="G861" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B862" t="s">
+        <v>7</v>
+      </c>
+      <c r="C862" t="s">
+        <v>7</v>
+      </c>
+      <c r="D862" t="s">
+        <v>8</v>
+      </c>
+      <c r="E862" t="s">
+        <v>9</v>
+      </c>
+      <c r="F862" s="1" t="n">
+        <v>45787</v>
+      </c>
+      <c r="G862" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B863" t="s">
+        <v>7</v>
+      </c>
+      <c r="C863" t="s">
+        <v>7</v>
+      </c>
+      <c r="D863" t="s">
+        <v>8</v>
+      </c>
+      <c r="E863" t="s">
+        <v>9</v>
+      </c>
+      <c r="F863" s="1" t="n">
+        <v>45788</v>
+      </c>
+      <c r="G863" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B864" t="s">
+        <v>7</v>
+      </c>
+      <c r="C864" t="s">
+        <v>7</v>
+      </c>
+      <c r="D864" t="s">
+        <v>8</v>
+      </c>
+      <c r="E864" t="s">
+        <v>9</v>
+      </c>
+      <c r="F864" s="1" t="n">
+        <v>45789</v>
+      </c>
+      <c r="G864" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B865" t="s">
+        <v>7</v>
+      </c>
+      <c r="C865" t="s">
+        <v>7</v>
+      </c>
+      <c r="D865" t="s">
+        <v>8</v>
+      </c>
+      <c r="E865" t="s">
+        <v>9</v>
+      </c>
+      <c r="F865" s="1" t="n">
+        <v>45790</v>
+      </c>
+      <c r="G865" t="n">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B866" t="s">
+        <v>7</v>
+      </c>
+      <c r="C866" t="s">
+        <v>7</v>
+      </c>
+      <c r="D866" t="s">
+        <v>8</v>
+      </c>
+      <c r="E866" t="s">
+        <v>9</v>
+      </c>
+      <c r="F866" s="1" t="n">
+        <v>45791</v>
+      </c>
+      <c r="G866" t="n">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B867" t="s">
+        <v>7</v>
+      </c>
+      <c r="C867" t="s">
+        <v>7</v>
+      </c>
+      <c r="D867" t="s">
+        <v>8</v>
+      </c>
+      <c r="E867" t="s">
+        <v>9</v>
+      </c>
+      <c r="F867" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="G867" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B868" t="s">
+        <v>7</v>
+      </c>
+      <c r="C868" t="s">
+        <v>7</v>
+      </c>
+      <c r="D868" t="s">
+        <v>8</v>
+      </c>
+      <c r="E868" t="s">
+        <v>9</v>
+      </c>
+      <c r="F868" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="G868" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B869" t="s">
+        <v>7</v>
+      </c>
+      <c r="C869" t="s">
+        <v>7</v>
+      </c>
+      <c r="D869" t="s">
+        <v>8</v>
+      </c>
+      <c r="E869" t="s">
+        <v>9</v>
+      </c>
+      <c r="F869" s="1" t="n">
+        <v>45794</v>
+      </c>
+      <c r="G869" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B870" t="s">
+        <v>7</v>
+      </c>
+      <c r="C870" t="s">
+        <v>7</v>
+      </c>
+      <c r="D870" t="s">
+        <v>8</v>
+      </c>
+      <c r="E870" t="s">
+        <v>9</v>
+      </c>
+      <c r="F870" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="G870" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B871" t="s">
+        <v>7</v>
+      </c>
+      <c r="C871" t="s">
+        <v>7</v>
+      </c>
+      <c r="D871" t="s">
+        <v>8</v>
+      </c>
+      <c r="E871" t="s">
+        <v>9</v>
+      </c>
+      <c r="F871" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="G871" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B872" t="s">
+        <v>7</v>
+      </c>
+      <c r="C872" t="s">
+        <v>7</v>
+      </c>
+      <c r="D872" t="s">
+        <v>8</v>
+      </c>
+      <c r="E872" t="s">
+        <v>9</v>
+      </c>
+      <c r="F872" s="1" t="n">
+        <v>45797</v>
+      </c>
+      <c r="G872" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B873" t="s">
+        <v>7</v>
+      </c>
+      <c r="C873" t="s">
+        <v>7</v>
+      </c>
+      <c r="D873" t="s">
+        <v>8</v>
+      </c>
+      <c r="E873" t="s">
+        <v>9</v>
+      </c>
+      <c r="F873" s="1" t="n">
+        <v>45798</v>
+      </c>
+      <c r="G873" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B874" t="s">
+        <v>7</v>
+      </c>
+      <c r="C874" t="s">
+        <v>7</v>
+      </c>
+      <c r="D874" t="s">
+        <v>8</v>
+      </c>
+      <c r="E874" t="s">
+        <v>9</v>
+      </c>
+      <c r="F874" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="G874" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B875" t="s">
+        <v>7</v>
+      </c>
+      <c r="C875" t="s">
+        <v>7</v>
+      </c>
+      <c r="D875" t="s">
+        <v>8</v>
+      </c>
+      <c r="E875" t="s">
+        <v>9</v>
+      </c>
+      <c r="F875" s="1" t="n">
+        <v>45800</v>
+      </c>
+      <c r="G875" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B876" t="s">
+        <v>7</v>
+      </c>
+      <c r="C876" t="s">
+        <v>7</v>
+      </c>
+      <c r="D876" t="s">
+        <v>8</v>
+      </c>
+      <c r="E876" t="s">
+        <v>9</v>
+      </c>
+      <c r="F876" s="1" t="n">
+        <v>45801</v>
+      </c>
+      <c r="G876" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B877" t="s">
+        <v>7</v>
+      </c>
+      <c r="C877" t="s">
+        <v>7</v>
+      </c>
+      <c r="D877" t="s">
+        <v>8</v>
+      </c>
+      <c r="E877" t="s">
+        <v>9</v>
+      </c>
+      <c r="F877" s="1" t="n">
+        <v>45802</v>
+      </c>
+      <c r="G877" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B878" t="s">
+        <v>7</v>
+      </c>
+      <c r="C878" t="s">
+        <v>7</v>
+      </c>
+      <c r="D878" t="s">
+        <v>8</v>
+      </c>
+      <c r="E878" t="s">
+        <v>9</v>
+      </c>
+      <c r="F878" s="1" t="n">
+        <v>45803</v>
+      </c>
+      <c r="G878" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B879" t="s">
+        <v>7</v>
+      </c>
+      <c r="C879" t="s">
+        <v>7</v>
+      </c>
+      <c r="D879" t="s">
+        <v>8</v>
+      </c>
+      <c r="E879" t="s">
+        <v>9</v>
+      </c>
+      <c r="F879" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="G879" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B880" t="s">
+        <v>7</v>
+      </c>
+      <c r="C880" t="s">
+        <v>7</v>
+      </c>
+      <c r="D880" t="s">
+        <v>8</v>
+      </c>
+      <c r="E880" t="s">
+        <v>9</v>
+      </c>
+      <c r="F880" s="1" t="n">
+        <v>45805</v>
+      </c>
+      <c r="G880" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B881" t="s">
+        <v>7</v>
+      </c>
+      <c r="C881" t="s">
+        <v>7</v>
+      </c>
+      <c r="D881" t="s">
+        <v>8</v>
+      </c>
+      <c r="E881" t="s">
+        <v>9</v>
+      </c>
+      <c r="F881" s="1" t="n">
+        <v>45806</v>
+      </c>
+      <c r="G881" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B882" t="s">
+        <v>7</v>
+      </c>
+      <c r="C882" t="s">
+        <v>7</v>
+      </c>
+      <c r="D882" t="s">
+        <v>8</v>
+      </c>
+      <c r="E882" t="s">
+        <v>9</v>
+      </c>
+      <c r="F882" s="1" t="n">
+        <v>45807</v>
+      </c>
+      <c r="G882" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B883" t="s">
+        <v>7</v>
+      </c>
+      <c r="C883" t="s">
+        <v>7</v>
+      </c>
+      <c r="D883" t="s">
+        <v>8</v>
+      </c>
+      <c r="E883" t="s">
+        <v>9</v>
+      </c>
+      <c r="F883" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="G883" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B884" t="s">
+        <v>7</v>
+      </c>
+      <c r="C884" t="s">
+        <v>7</v>
+      </c>
+      <c r="D884" t="s">
+        <v>8</v>
+      </c>
+      <c r="E884" t="s">
+        <v>9</v>
+      </c>
+      <c r="F884" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="G884" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B885" t="s">
+        <v>7</v>
+      </c>
+      <c r="C885" t="s">
+        <v>7</v>
+      </c>
+      <c r="D885" t="s">
+        <v>8</v>
+      </c>
+      <c r="E885" t="s">
+        <v>9</v>
+      </c>
+      <c r="F885" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G885" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B886" t="s">
+        <v>7</v>
+      </c>
+      <c r="C886" t="s">
+        <v>7</v>
+      </c>
+      <c r="D886" t="s">
+        <v>8</v>
+      </c>
+      <c r="E886" t="s">
+        <v>9</v>
+      </c>
+      <c r="F886" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="G886" t="n">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B887" t="s">
+        <v>7</v>
+      </c>
+      <c r="C887" t="s">
+        <v>7</v>
+      </c>
+      <c r="D887" t="s">
+        <v>8</v>
+      </c>
+      <c r="E887" t="s">
+        <v>9</v>
+      </c>
+      <c r="F887" s="1" t="n">
+        <v>45812</v>
+      </c>
+      <c r="G887" t="n">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B888" t="s">
+        <v>7</v>
+      </c>
+      <c r="C888" t="s">
+        <v>7</v>
+      </c>
+      <c r="D888" t="s">
+        <v>8</v>
+      </c>
+      <c r="E888" t="s">
+        <v>9</v>
+      </c>
+      <c r="F888" s="1" t="n">
+        <v>45813</v>
+      </c>
+      <c r="G888" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B889" t="s">
+        <v>7</v>
+      </c>
+      <c r="C889" t="s">
+        <v>7</v>
+      </c>
+      <c r="D889" t="s">
+        <v>8</v>
+      </c>
+      <c r="E889" t="s">
+        <v>9</v>
+      </c>
+      <c r="F889" s="1" t="n">
+        <v>45814</v>
+      </c>
+      <c r="G889" t="n">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B890" t="s">
+        <v>7</v>
+      </c>
+      <c r="C890" t="s">
+        <v>7</v>
+      </c>
+      <c r="D890" t="s">
+        <v>8</v>
+      </c>
+      <c r="E890" t="s">
+        <v>9</v>
+      </c>
+      <c r="F890" s="1" t="n">
+        <v>45815</v>
+      </c>
+      <c r="G890" t="n">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B891" t="s">
+        <v>7</v>
+      </c>
+      <c r="C891" t="s">
+        <v>7</v>
+      </c>
+      <c r="D891" t="s">
+        <v>8</v>
+      </c>
+      <c r="E891" t="s">
+        <v>9</v>
+      </c>
+      <c r="F891" s="1" t="n">
+        <v>45816</v>
+      </c>
+      <c r="G891" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B892" t="s">
+        <v>7</v>
+      </c>
+      <c r="C892" t="s">
+        <v>7</v>
+      </c>
+      <c r="D892" t="s">
+        <v>8</v>
+      </c>
+      <c r="E892" t="s">
+        <v>9</v>
+      </c>
+      <c r="F892" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G892" t="n">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B893" t="s">
+        <v>7</v>
+      </c>
+      <c r="C893" t="s">
+        <v>7</v>
+      </c>
+      <c r="D893" t="s">
+        <v>8</v>
+      </c>
+      <c r="E893" t="s">
+        <v>9</v>
+      </c>
+      <c r="F893" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="G893" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B894" t="s">
+        <v>7</v>
+      </c>
+      <c r="C894" t="s">
+        <v>7</v>
+      </c>
+      <c r="D894" t="s">
+        <v>8</v>
+      </c>
+      <c r="E894" t="s">
+        <v>9</v>
+      </c>
+      <c r="F894" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="G894" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B895" t="s">
+        <v>7</v>
+      </c>
+      <c r="C895" t="s">
+        <v>7</v>
+      </c>
+      <c r="D895" t="s">
+        <v>8</v>
+      </c>
+      <c r="E895" t="s">
+        <v>9</v>
+      </c>
+      <c r="F895" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="G895" t="n">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B896" t="s">
+        <v>7</v>
+      </c>
+      <c r="C896" t="s">
+        <v>7</v>
+      </c>
+      <c r="D896" t="s">
+        <v>8</v>
+      </c>
+      <c r="E896" t="s">
+        <v>9</v>
+      </c>
+      <c r="F896" s="1" t="n">
+        <v>45821</v>
+      </c>
+      <c r="G896" t="n">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B897" t="s">
+        <v>7</v>
+      </c>
+      <c r="C897" t="s">
+        <v>7</v>
+      </c>
+      <c r="D897" t="s">
+        <v>8</v>
+      </c>
+      <c r="E897" t="s">
+        <v>9</v>
+      </c>
+      <c r="F897" s="1" t="n">
+        <v>45822</v>
+      </c>
+      <c r="G897" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B898" t="s">
+        <v>7</v>
+      </c>
+      <c r="C898" t="s">
+        <v>7</v>
+      </c>
+      <c r="D898" t="s">
+        <v>8</v>
+      </c>
+      <c r="E898" t="s">
+        <v>9</v>
+      </c>
+      <c r="F898" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="G898" t="n">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B899" t="s">
+        <v>7</v>
+      </c>
+      <c r="C899" t="s">
+        <v>7</v>
+      </c>
+      <c r="D899" t="s">
+        <v>8</v>
+      </c>
+      <c r="E899" t="s">
+        <v>9</v>
+      </c>
+      <c r="F899" s="1" t="n">
+        <v>45824</v>
+      </c>
+      <c r="G899" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B900" t="s">
+        <v>7</v>
+      </c>
+      <c r="C900" t="s">
+        <v>7</v>
+      </c>
+      <c r="D900" t="s">
+        <v>8</v>
+      </c>
+      <c r="E900" t="s">
+        <v>9</v>
+      </c>
+      <c r="F900" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="G900" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B901" t="s">
+        <v>7</v>
+      </c>
+      <c r="C901" t="s">
+        <v>7</v>
+      </c>
+      <c r="D901" t="s">
+        <v>8</v>
+      </c>
+      <c r="E901" t="s">
+        <v>9</v>
+      </c>
+      <c r="F901" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G901" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B902" t="s">
+        <v>7</v>
+      </c>
+      <c r="C902" t="s">
+        <v>7</v>
+      </c>
+      <c r="D902" t="s">
+        <v>8</v>
+      </c>
+      <c r="E902" t="s">
+        <v>9</v>
+      </c>
+      <c r="F902" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="G902" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B903" t="s">
+        <v>7</v>
+      </c>
+      <c r="C903" t="s">
+        <v>7</v>
+      </c>
+      <c r="D903" t="s">
+        <v>8</v>
+      </c>
+      <c r="E903" t="s">
+        <v>9</v>
+      </c>
+      <c r="F903" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="G903" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B904" t="s">
+        <v>7</v>
+      </c>
+      <c r="C904" t="s">
+        <v>7</v>
+      </c>
+      <c r="D904" t="s">
+        <v>8</v>
+      </c>
+      <c r="E904" t="s">
+        <v>9</v>
+      </c>
+      <c r="F904" s="1" t="n">
+        <v>45829</v>
+      </c>
+      <c r="G904" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B905" t="s">
+        <v>7</v>
+      </c>
+      <c r="C905" t="s">
+        <v>7</v>
+      </c>
+      <c r="D905" t="s">
+        <v>8</v>
+      </c>
+      <c r="E905" t="s">
+        <v>9</v>
+      </c>
+      <c r="F905" s="1" t="n">
+        <v>45830</v>
+      </c>
+      <c r="G905" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B906" t="s">
+        <v>7</v>
+      </c>
+      <c r="C906" t="s">
+        <v>7</v>
+      </c>
+      <c r="D906" t="s">
+        <v>8</v>
+      </c>
+      <c r="E906" t="s">
+        <v>9</v>
+      </c>
+      <c r="F906" s="1" t="n">
+        <v>45831</v>
+      </c>
+      <c r="G906" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B907" t="s">
+        <v>7</v>
+      </c>
+      <c r="C907" t="s">
+        <v>7</v>
+      </c>
+      <c r="D907" t="s">
+        <v>8</v>
+      </c>
+      <c r="E907" t="s">
+        <v>9</v>
+      </c>
+      <c r="F907" s="1" t="n">
+        <v>45832</v>
+      </c>
+      <c r="G907" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B908" t="s">
+        <v>7</v>
+      </c>
+      <c r="C908" t="s">
+        <v>7</v>
+      </c>
+      <c r="D908" t="s">
+        <v>8</v>
+      </c>
+      <c r="E908" t="s">
+        <v>9</v>
+      </c>
+      <c r="F908" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="G908" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B909" t="s">
+        <v>7</v>
+      </c>
+      <c r="C909" t="s">
+        <v>7</v>
+      </c>
+      <c r="D909" t="s">
+        <v>8</v>
+      </c>
+      <c r="E909" t="s">
+        <v>9</v>
+      </c>
+      <c r="F909" s="1" t="n">
+        <v>45834</v>
+      </c>
+      <c r="G909" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B910" t="s">
+        <v>7</v>
+      </c>
+      <c r="C910" t="s">
+        <v>7</v>
+      </c>
+      <c r="D910" t="s">
+        <v>8</v>
+      </c>
+      <c r="E910" t="s">
+        <v>9</v>
+      </c>
+      <c r="F910" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G910" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B911" t="s">
+        <v>7</v>
+      </c>
+      <c r="C911" t="s">
+        <v>7</v>
+      </c>
+      <c r="D911" t="s">
+        <v>8</v>
+      </c>
+      <c r="E911" t="s">
+        <v>9</v>
+      </c>
+      <c r="F911" s="1" t="n">
+        <v>45836</v>
+      </c>
+      <c r="G911" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B912" t="s">
+        <v>7</v>
+      </c>
+      <c r="C912" t="s">
+        <v>7</v>
+      </c>
+      <c r="D912" t="s">
+        <v>8</v>
+      </c>
+      <c r="E912" t="s">
+        <v>9</v>
+      </c>
+      <c r="F912" s="1" t="n">
+        <v>45837</v>
+      </c>
+      <c r="G912" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B913" t="s">
+        <v>7</v>
+      </c>
+      <c r="C913" t="s">
+        <v>7</v>
+      </c>
+      <c r="D913" t="s">
+        <v>8</v>
+      </c>
+      <c r="E913" t="s">
+        <v>9</v>
+      </c>
+      <c r="F913" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="G913" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B914" t="s">
+        <v>7</v>
+      </c>
+      <c r="C914" t="s">
+        <v>7</v>
+      </c>
+      <c r="D914" t="s">
+        <v>8</v>
+      </c>
+      <c r="E914" t="s">
+        <v>9</v>
+      </c>
+      <c r="F914" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="G914" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B915" t="s">
+        <v>7</v>
+      </c>
+      <c r="C915" t="s">
+        <v>7</v>
+      </c>
+      <c r="D915" t="s">
+        <v>8</v>
+      </c>
+      <c r="E915" t="s">
+        <v>9</v>
+      </c>
+      <c r="F915" s="1" t="n">
+        <v>45840</v>
+      </c>
+      <c r="G915" t="n">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B916" t="s">
+        <v>7</v>
+      </c>
+      <c r="C916" t="s">
+        <v>7</v>
+      </c>
+      <c r="D916" t="s">
+        <v>8</v>
+      </c>
+      <c r="E916" t="s">
+        <v>9</v>
+      </c>
+      <c r="F916" s="1" t="n">
+        <v>45841</v>
+      </c>
+      <c r="G916" t="n">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B917" t="s">
+        <v>7</v>
+      </c>
+      <c r="C917" t="s">
+        <v>7</v>
+      </c>
+      <c r="D917" t="s">
+        <v>8</v>
+      </c>
+      <c r="E917" t="s">
+        <v>9</v>
+      </c>
+      <c r="F917" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G917" t="n">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B918" t="s">
+        <v>7</v>
+      </c>
+      <c r="C918" t="s">
+        <v>7</v>
+      </c>
+      <c r="D918" t="s">
+        <v>8</v>
+      </c>
+      <c r="E918" t="s">
+        <v>9</v>
+      </c>
+      <c r="F918" s="1" t="n">
+        <v>45843</v>
+      </c>
+      <c r="G918" t="n">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B919" t="s">
+        <v>7</v>
+      </c>
+      <c r="C919" t="s">
+        <v>7</v>
+      </c>
+      <c r="D919" t="s">
+        <v>8</v>
+      </c>
+      <c r="E919" t="s">
+        <v>9</v>
+      </c>
+      <c r="F919" s="1" t="n">
+        <v>45844</v>
+      </c>
+      <c r="G919" t="n">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B920" t="s">
+        <v>7</v>
+      </c>
+      <c r="C920" t="s">
+        <v>7</v>
+      </c>
+      <c r="D920" t="s">
+        <v>8</v>
+      </c>
+      <c r="E920" t="s">
+        <v>9</v>
+      </c>
+      <c r="F920" s="1" t="n">
+        <v>45845</v>
+      </c>
+      <c r="G920" t="n">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B921" t="s">
+        <v>7</v>
+      </c>
+      <c r="C921" t="s">
+        <v>7</v>
+      </c>
+      <c r="D921" t="s">
+        <v>8</v>
+      </c>
+      <c r="E921" t="s">
+        <v>9</v>
+      </c>
+      <c r="F921" s="1" t="n">
+        <v>45846</v>
+      </c>
+      <c r="G921" t="n">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B922" t="s">
+        <v>7</v>
+      </c>
+      <c r="C922" t="s">
+        <v>7</v>
+      </c>
+      <c r="D922" t="s">
+        <v>8</v>
+      </c>
+      <c r="E922" t="s">
+        <v>9</v>
+      </c>
+      <c r="F922" s="1" t="n">
+        <v>45847</v>
+      </c>
+      <c r="G922" t="n">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B923" t="s">
+        <v>7</v>
+      </c>
+      <c r="C923" t="s">
+        <v>7</v>
+      </c>
+      <c r="D923" t="s">
+        <v>8</v>
+      </c>
+      <c r="E923" t="s">
+        <v>9</v>
+      </c>
+      <c r="F923" s="1" t="n">
+        <v>45848</v>
+      </c>
+      <c r="G923" t="n">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B924" t="s">
+        <v>7</v>
+      </c>
+      <c r="C924" t="s">
+        <v>7</v>
+      </c>
+      <c r="D924" t="s">
+        <v>8</v>
+      </c>
+      <c r="E924" t="s">
+        <v>9</v>
+      </c>
+      <c r="F924" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G924" t="n">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B925" t="s">
+        <v>7</v>
+      </c>
+      <c r="C925" t="s">
+        <v>7</v>
+      </c>
+      <c r="D925" t="s">
+        <v>8</v>
+      </c>
+      <c r="E925" t="s">
+        <v>9</v>
+      </c>
+      <c r="F925" s="1" t="n">
+        <v>45850</v>
+      </c>
+      <c r="G925" t="n">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B926" t="s">
+        <v>7</v>
+      </c>
+      <c r="C926" t="s">
+        <v>7</v>
+      </c>
+      <c r="D926" t="s">
+        <v>8</v>
+      </c>
+      <c r="E926" t="s">
+        <v>9</v>
+      </c>
+      <c r="F926" s="1" t="n">
+        <v>45851</v>
+      </c>
+      <c r="G926" t="n">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B927" t="s">
+        <v>7</v>
+      </c>
+      <c r="C927" t="s">
+        <v>7</v>
+      </c>
+      <c r="D927" t="s">
+        <v>8</v>
+      </c>
+      <c r="E927" t="s">
+        <v>9</v>
+      </c>
+      <c r="F927" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="G927" t="n">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B928" t="s">
+        <v>7</v>
+      </c>
+      <c r="C928" t="s">
+        <v>7</v>
+      </c>
+      <c r="D928" t="s">
+        <v>8</v>
+      </c>
+      <c r="E928" t="s">
+        <v>9</v>
+      </c>
+      <c r="F928" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="G928" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B929" t="s">
+        <v>7</v>
+      </c>
+      <c r="C929" t="s">
+        <v>7</v>
+      </c>
+      <c r="D929" t="s">
+        <v>8</v>
+      </c>
+      <c r="E929" t="s">
+        <v>9</v>
+      </c>
+      <c r="F929" s="1" t="n">
+        <v>45854</v>
+      </c>
+      <c r="G929" t="n">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B930" t="s">
+        <v>7</v>
+      </c>
+      <c r="C930" t="s">
+        <v>7</v>
+      </c>
+      <c r="D930" t="s">
+        <v>8</v>
+      </c>
+      <c r="E930" t="s">
+        <v>9</v>
+      </c>
+      <c r="F930" s="1" t="n">
+        <v>45855</v>
+      </c>
+      <c r="G930" t="n">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B931" t="s">
+        <v>7</v>
+      </c>
+      <c r="C931" t="s">
+        <v>7</v>
+      </c>
+      <c r="D931" t="s">
+        <v>8</v>
+      </c>
+      <c r="E931" t="s">
+        <v>9</v>
+      </c>
+      <c r="F931" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G931" t="n">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B932" t="s">
+        <v>7</v>
+      </c>
+      <c r="C932" t="s">
+        <v>7</v>
+      </c>
+      <c r="D932" t="s">
+        <v>8</v>
+      </c>
+      <c r="E932" t="s">
+        <v>9</v>
+      </c>
+      <c r="F932" s="1" t="n">
+        <v>45857</v>
+      </c>
+      <c r="G932" t="n">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B933" t="s">
+        <v>7</v>
+      </c>
+      <c r="C933" t="s">
+        <v>7</v>
+      </c>
+      <c r="D933" t="s">
+        <v>8</v>
+      </c>
+      <c r="E933" t="s">
+        <v>9</v>
+      </c>
+      <c r="F933" s="1" t="n">
+        <v>45858</v>
+      </c>
+      <c r="G933" t="n">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B934" t="s">
+        <v>7</v>
+      </c>
+      <c r="C934" t="s">
+        <v>7</v>
+      </c>
+      <c r="D934" t="s">
+        <v>8</v>
+      </c>
+      <c r="E934" t="s">
+        <v>9</v>
+      </c>
+      <c r="F934" s="1" t="n">
+        <v>45859</v>
+      </c>
+      <c r="G934" t="n">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B935" t="s">
+        <v>7</v>
+      </c>
+      <c r="C935" t="s">
+        <v>7</v>
+      </c>
+      <c r="D935" t="s">
+        <v>8</v>
+      </c>
+      <c r="E935" t="s">
+        <v>9</v>
+      </c>
+      <c r="F935" s="1" t="n">
+        <v>45860</v>
+      </c>
+      <c r="G935" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B936" t="s">
+        <v>7</v>
+      </c>
+      <c r="C936" t="s">
+        <v>7</v>
+      </c>
+      <c r="D936" t="s">
+        <v>8</v>
+      </c>
+      <c r="E936" t="s">
+        <v>9</v>
+      </c>
+      <c r="F936" s="1" t="n">
+        <v>45861</v>
+      </c>
+      <c r="G936" t="n">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B937" t="s">
+        <v>7</v>
+      </c>
+      <c r="C937" t="s">
+        <v>7</v>
+      </c>
+      <c r="D937" t="s">
+        <v>8</v>
+      </c>
+      <c r="E937" t="s">
+        <v>9</v>
+      </c>
+      <c r="F937" s="1" t="n">
+        <v>45862</v>
+      </c>
+      <c r="G937" t="n">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B938" t="s">
+        <v>7</v>
+      </c>
+      <c r="C938" t="s">
+        <v>7</v>
+      </c>
+      <c r="D938" t="s">
+        <v>8</v>
+      </c>
+      <c r="E938" t="s">
+        <v>9</v>
+      </c>
+      <c r="F938" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G938" t="n">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B939" t="s">
+        <v>7</v>
+      </c>
+      <c r="C939" t="s">
+        <v>7</v>
+      </c>
+      <c r="D939" t="s">
+        <v>8</v>
+      </c>
+      <c r="E939" t="s">
+        <v>9</v>
+      </c>
+      <c r="F939" s="1" t="n">
+        <v>45864</v>
+      </c>
+      <c r="G939" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B940" t="s">
+        <v>7</v>
+      </c>
+      <c r="C940" t="s">
+        <v>7</v>
+      </c>
+      <c r="D940" t="s">
+        <v>8</v>
+      </c>
+      <c r="E940" t="s">
+        <v>9</v>
+      </c>
+      <c r="F940" s="1" t="n">
+        <v>45865</v>
+      </c>
+      <c r="G940" t="n">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B941" t="s">
+        <v>7</v>
+      </c>
+      <c r="C941" t="s">
+        <v>7</v>
+      </c>
+      <c r="D941" t="s">
+        <v>8</v>
+      </c>
+      <c r="E941" t="s">
+        <v>9</v>
+      </c>
+      <c r="F941" s="1" t="n">
+        <v>45866</v>
+      </c>
+      <c r="G941" t="n">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B942" t="s">
+        <v>7</v>
+      </c>
+      <c r="C942" t="s">
+        <v>7</v>
+      </c>
+      <c r="D942" t="s">
+        <v>8</v>
+      </c>
+      <c r="E942" t="s">
+        <v>9</v>
+      </c>
+      <c r="F942" s="1" t="n">
+        <v>45867</v>
+      </c>
+      <c r="G942" t="n">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B943" t="s">
+        <v>7</v>
+      </c>
+      <c r="C943" t="s">
+        <v>7</v>
+      </c>
+      <c r="D943" t="s">
+        <v>8</v>
+      </c>
+      <c r="E943" t="s">
+        <v>9</v>
+      </c>
+      <c r="F943" s="1" t="n">
+        <v>45868</v>
+      </c>
+      <c r="G943" t="n">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B944" t="s">
+        <v>7</v>
+      </c>
+      <c r="C944" t="s">
+        <v>7</v>
+      </c>
+      <c r="D944" t="s">
+        <v>8</v>
+      </c>
+      <c r="E944" t="s">
+        <v>9</v>
+      </c>
+      <c r="F944" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="G944" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B945" t="s">
+        <v>7</v>
+      </c>
+      <c r="C945" t="s">
+        <v>7</v>
+      </c>
+      <c r="D945" t="s">
+        <v>8</v>
+      </c>
+      <c r="E945" t="s">
+        <v>9</v>
+      </c>
+      <c r="F945" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="G945" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B946" t="s">
+        <v>7</v>
+      </c>
+      <c r="C946" t="s">
+        <v>7</v>
+      </c>
+      <c r="D946" t="s">
+        <v>8</v>
+      </c>
+      <c r="E946" t="s">
+        <v>9</v>
+      </c>
+      <c r="F946" s="1" t="n">
+        <v>45871</v>
+      </c>
+      <c r="G946" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B947" t="s">
+        <v>7</v>
+      </c>
+      <c r="C947" t="s">
+        <v>7</v>
+      </c>
+      <c r="D947" t="s">
+        <v>8</v>
+      </c>
+      <c r="E947" t="s">
+        <v>9</v>
+      </c>
+      <c r="F947" s="1" t="n">
+        <v>45872</v>
+      </c>
+      <c r="G947" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B948" t="s">
+        <v>7</v>
+      </c>
+      <c r="C948" t="s">
+        <v>7</v>
+      </c>
+      <c r="D948" t="s">
+        <v>8</v>
+      </c>
+      <c r="E948" t="s">
+        <v>9</v>
+      </c>
+      <c r="F948" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G948" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B949" t="s">
+        <v>7</v>
+      </c>
+      <c r="C949" t="s">
+        <v>7</v>
+      </c>
+      <c r="D949" t="s">
+        <v>8</v>
+      </c>
+      <c r="E949" t="s">
+        <v>9</v>
+      </c>
+      <c r="F949" s="1" t="n">
+        <v>45874</v>
+      </c>
+      <c r="G949" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B950" t="s">
+        <v>7</v>
+      </c>
+      <c r="C950" t="s">
+        <v>7</v>
+      </c>
+      <c r="D950" t="s">
+        <v>8</v>
+      </c>
+      <c r="E950" t="s">
+        <v>9</v>
+      </c>
+      <c r="F950" s="1" t="n">
+        <v>45875</v>
+      </c>
+      <c r="G950" t="n">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B951" t="s">
+        <v>7</v>
+      </c>
+      <c r="C951" t="s">
+        <v>7</v>
+      </c>
+      <c r="D951" t="s">
+        <v>8</v>
+      </c>
+      <c r="E951" t="s">
+        <v>9</v>
+      </c>
+      <c r="F951" s="1" t="n">
+        <v>45876</v>
+      </c>
+      <c r="G951" t="n">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B952" t="s">
+        <v>7</v>
+      </c>
+      <c r="C952" t="s">
+        <v>7</v>
+      </c>
+      <c r="D952" t="s">
+        <v>8</v>
+      </c>
+      <c r="E952" t="s">
+        <v>9</v>
+      </c>
+      <c r="F952" s="1" t="n">
+        <v>45877</v>
+      </c>
+      <c r="G952" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B953" t="s">
+        <v>7</v>
+      </c>
+      <c r="C953" t="s">
+        <v>7</v>
+      </c>
+      <c r="D953" t="s">
+        <v>8</v>
+      </c>
+      <c r="E953" t="s">
+        <v>9</v>
+      </c>
+      <c r="F953" s="1" t="n">
+        <v>45878</v>
+      </c>
+      <c r="G953" t="n">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B954" t="s">
+        <v>7</v>
+      </c>
+      <c r="C954" t="s">
+        <v>7</v>
+      </c>
+      <c r="D954" t="s">
+        <v>8</v>
+      </c>
+      <c r="E954" t="s">
+        <v>9</v>
+      </c>
+      <c r="F954" s="1" t="n">
+        <v>45879</v>
+      </c>
+      <c r="G954" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B955" t="s">
+        <v>7</v>
+      </c>
+      <c r="C955" t="s">
+        <v>7</v>
+      </c>
+      <c r="D955" t="s">
+        <v>8</v>
+      </c>
+      <c r="E955" t="s">
+        <v>9</v>
+      </c>
+      <c r="F955" s="1" t="n">
+        <v>45880</v>
+      </c>
+      <c r="G955" t="n">
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B956" t="s">
+        <v>7</v>
+      </c>
+      <c r="C956" t="s">
+        <v>7</v>
+      </c>
+      <c r="D956" t="s">
+        <v>8</v>
+      </c>
+      <c r="E956" t="s">
+        <v>9</v>
+      </c>
+      <c r="F956" s="1" t="n">
+        <v>45881</v>
+      </c>
+      <c r="G956" t="n">
+        <v>3422</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B957" t="s">
+        <v>7</v>
+      </c>
+      <c r="C957" t="s">
+        <v>7</v>
+      </c>
+      <c r="D957" t="s">
+        <v>8</v>
+      </c>
+      <c r="E957" t="s">
+        <v>9</v>
+      </c>
+      <c r="F957" s="1" t="n">
+        <v>45882</v>
+      </c>
+      <c r="G957" t="n">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B958" t="s">
+        <v>7</v>
+      </c>
+      <c r="C958" t="s">
+        <v>7</v>
+      </c>
+      <c r="D958" t="s">
+        <v>8</v>
+      </c>
+      <c r="E958" t="s">
+        <v>9</v>
+      </c>
+      <c r="F958" s="1" t="n">
+        <v>45883</v>
+      </c>
+      <c r="G958" t="n">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B959" t="s">
+        <v>7</v>
+      </c>
+      <c r="C959" t="s">
+        <v>7</v>
+      </c>
+      <c r="D959" t="s">
+        <v>8</v>
+      </c>
+      <c r="E959" t="s">
+        <v>9</v>
+      </c>
+      <c r="F959" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="G959" t="n">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B960" t="s">
+        <v>7</v>
+      </c>
+      <c r="C960" t="s">
+        <v>7</v>
+      </c>
+      <c r="D960" t="s">
+        <v>8</v>
+      </c>
+      <c r="E960" t="s">
+        <v>9</v>
+      </c>
+      <c r="F960" s="1" t="n">
+        <v>45885</v>
+      </c>
+      <c r="G960" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B961" t="s">
+        <v>7</v>
+      </c>
+      <c r="C961" t="s">
+        <v>7</v>
+      </c>
+      <c r="D961" t="s">
+        <v>8</v>
+      </c>
+      <c r="E961" t="s">
+        <v>9</v>
+      </c>
+      <c r="F961" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="G961" t="n">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B962" t="s">
+        <v>7</v>
+      </c>
+      <c r="C962" t="s">
+        <v>7</v>
+      </c>
+      <c r="D962" t="s">
+        <v>8</v>
+      </c>
+      <c r="E962" t="s">
+        <v>9</v>
+      </c>
+      <c r="F962" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="G962" t="n">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B963" t="s">
+        <v>7</v>
+      </c>
+      <c r="C963" t="s">
+        <v>7</v>
+      </c>
+      <c r="D963" t="s">
+        <v>8</v>
+      </c>
+      <c r="E963" t="s">
+        <v>9</v>
+      </c>
+      <c r="F963" s="1" t="n">
+        <v>45888</v>
+      </c>
+      <c r="G963" t="n">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B964" t="s">
+        <v>7</v>
+      </c>
+      <c r="C964" t="s">
+        <v>7</v>
+      </c>
+      <c r="D964" t="s">
+        <v>8</v>
+      </c>
+      <c r="E964" t="s">
+        <v>9</v>
+      </c>
+      <c r="F964" s="1" t="n">
+        <v>45889</v>
+      </c>
+      <c r="G964" t="n">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B965" t="s">
+        <v>7</v>
+      </c>
+      <c r="C965" t="s">
+        <v>7</v>
+      </c>
+      <c r="D965" t="s">
+        <v>8</v>
+      </c>
+      <c r="E965" t="s">
+        <v>9</v>
+      </c>
+      <c r="F965" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="G965" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B966" t="s">
+        <v>7</v>
+      </c>
+      <c r="C966" t="s">
+        <v>7</v>
+      </c>
+      <c r="D966" t="s">
+        <v>8</v>
+      </c>
+      <c r="E966" t="s">
+        <v>9</v>
+      </c>
+      <c r="F966" s="1" t="n">
+        <v>45891</v>
+      </c>
+      <c r="G966" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B967" t="s">
+        <v>7</v>
+      </c>
+      <c r="C967" t="s">
+        <v>7</v>
+      </c>
+      <c r="D967" t="s">
+        <v>8</v>
+      </c>
+      <c r="E967" t="s">
+        <v>9</v>
+      </c>
+      <c r="F967" s="1" t="n">
+        <v>45892</v>
+      </c>
+      <c r="G967" t="n">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B968" t="s">
+        <v>7</v>
+      </c>
+      <c r="C968" t="s">
+        <v>7</v>
+      </c>
+      <c r="D968" t="s">
+        <v>8</v>
+      </c>
+      <c r="E968" t="s">
+        <v>9</v>
+      </c>
+      <c r="F968" s="1" t="n">
+        <v>45893</v>
+      </c>
+      <c r="G968" t="n">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B969" t="s">
+        <v>7</v>
+      </c>
+      <c r="C969" t="s">
+        <v>7</v>
+      </c>
+      <c r="D969" t="s">
+        <v>8</v>
+      </c>
+      <c r="E969" t="s">
+        <v>9</v>
+      </c>
+      <c r="F969" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="G969" t="n">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B970" t="s">
+        <v>7</v>
+      </c>
+      <c r="C970" t="s">
+        <v>7</v>
+      </c>
+      <c r="D970" t="s">
+        <v>8</v>
+      </c>
+      <c r="E970" t="s">
+        <v>9</v>
+      </c>
+      <c r="F970" s="1" t="n">
+        <v>45895</v>
+      </c>
+      <c r="G970" t="n">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B971" t="s">
+        <v>7</v>
+      </c>
+      <c r="C971" t="s">
+        <v>7</v>
+      </c>
+      <c r="D971" t="s">
+        <v>8</v>
+      </c>
+      <c r="E971" t="s">
+        <v>9</v>
+      </c>
+      <c r="F971" s="1" t="n">
+        <v>45896</v>
+      </c>
+      <c r="G971" t="n">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B972" t="s">
+        <v>7</v>
+      </c>
+      <c r="C972" t="s">
+        <v>7</v>
+      </c>
+      <c r="D972" t="s">
+        <v>8</v>
+      </c>
+      <c r="E972" t="s">
+        <v>9</v>
+      </c>
+      <c r="F972" s="1" t="n">
+        <v>45897</v>
+      </c>
+      <c r="G972" t="n">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B973" t="s">
+        <v>7</v>
+      </c>
+      <c r="C973" t="s">
+        <v>7</v>
+      </c>
+      <c r="D973" t="s">
+        <v>8</v>
+      </c>
+      <c r="E973" t="s">
+        <v>9</v>
+      </c>
+      <c r="F973" s="1" t="n">
+        <v>45898</v>
+      </c>
+      <c r="G973" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B974" t="s">
+        <v>7</v>
+      </c>
+      <c r="C974" t="s">
+        <v>7</v>
+      </c>
+      <c r="D974" t="s">
+        <v>8</v>
+      </c>
+      <c r="E974" t="s">
+        <v>9</v>
+      </c>
+      <c r="F974" s="1" t="n">
+        <v>45899</v>
+      </c>
+      <c r="G974" t="n">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B975" t="s">
+        <v>7</v>
+      </c>
+      <c r="C975" t="s">
+        <v>7</v>
+      </c>
+      <c r="D975" t="s">
+        <v>8</v>
+      </c>
+      <c r="E975" t="s">
+        <v>9</v>
+      </c>
+      <c r="F975" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="G975" t="n">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B976" t="s">
+        <v>7</v>
+      </c>
+      <c r="C976" t="s">
+        <v>7</v>
+      </c>
+      <c r="D976" t="s">
+        <v>8</v>
+      </c>
+      <c r="E976" t="s">
+        <v>9</v>
+      </c>
+      <c r="F976" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="G976" t="n">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B977" t="s">
+        <v>7</v>
+      </c>
+      <c r="C977" t="s">
+        <v>7</v>
+      </c>
+      <c r="D977" t="s">
+        <v>8</v>
+      </c>
+      <c r="E977" t="s">
+        <v>9</v>
+      </c>
+      <c r="F977" s="1" t="n">
+        <v>45902</v>
+      </c>
+      <c r="G977" t="n">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B978" t="s">
+        <v>7</v>
+      </c>
+      <c r="C978" t="s">
+        <v>7</v>
+      </c>
+      <c r="D978" t="s">
+        <v>8</v>
+      </c>
+      <c r="E978" t="s">
+        <v>9</v>
+      </c>
+      <c r="F978" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="G978" t="n">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B979" t="s">
+        <v>7</v>
+      </c>
+      <c r="C979" t="s">
+        <v>7</v>
+      </c>
+      <c r="D979" t="s">
+        <v>8</v>
+      </c>
+      <c r="E979" t="s">
+        <v>9</v>
+      </c>
+      <c r="F979" s="1" t="n">
+        <v>45904</v>
+      </c>
+      <c r="G979" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B980" t="s">
+        <v>7</v>
+      </c>
+      <c r="C980" t="s">
+        <v>7</v>
+      </c>
+      <c r="D980" t="s">
+        <v>8</v>
+      </c>
+      <c r="E980" t="s">
+        <v>9</v>
+      </c>
+      <c r="F980" s="1" t="n">
+        <v>45905</v>
+      </c>
+      <c r="G980" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B981" t="s">
+        <v>7</v>
+      </c>
+      <c r="C981" t="s">
+        <v>7</v>
+      </c>
+      <c r="D981" t="s">
+        <v>8</v>
+      </c>
+      <c r="E981" t="s">
+        <v>9</v>
+      </c>
+      <c r="F981" s="1" t="n">
+        <v>45906</v>
+      </c>
+      <c r="G981" t="n">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B982" t="s">
+        <v>7</v>
+      </c>
+      <c r="C982" t="s">
+        <v>7</v>
+      </c>
+      <c r="D982" t="s">
+        <v>8</v>
+      </c>
+      <c r="E982" t="s">
+        <v>9</v>
+      </c>
+      <c r="F982" s="1" t="n">
+        <v>45907</v>
+      </c>
+      <c r="G982" t="n">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B983" t="s">
+        <v>7</v>
+      </c>
+      <c r="C983" t="s">
+        <v>7</v>
+      </c>
+      <c r="D983" t="s">
+        <v>8</v>
+      </c>
+      <c r="E983" t="s">
+        <v>9</v>
+      </c>
+      <c r="F983" s="1" t="n">
+        <v>45908</v>
+      </c>
+      <c r="G983" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B984" t="s">
+        <v>7</v>
+      </c>
+      <c r="C984" t="s">
+        <v>7</v>
+      </c>
+      <c r="D984" t="s">
+        <v>8</v>
+      </c>
+      <c r="E984" t="s">
+        <v>9</v>
+      </c>
+      <c r="F984" s="1" t="n">
+        <v>45909</v>
+      </c>
+      <c r="G984" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B985" t="s">
+        <v>7</v>
+      </c>
+      <c r="C985" t="s">
+        <v>7</v>
+      </c>
+      <c r="D985" t="s">
+        <v>8</v>
+      </c>
+      <c r="E985" t="s">
+        <v>9</v>
+      </c>
+      <c r="F985" s="1" t="n">
+        <v>45910</v>
+      </c>
+      <c r="G985" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B986" t="s">
+        <v>7</v>
+      </c>
+      <c r="C986" t="s">
+        <v>7</v>
+      </c>
+      <c r="D986" t="s">
+        <v>8</v>
+      </c>
+      <c r="E986" t="s">
+        <v>9</v>
+      </c>
+      <c r="F986" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="G986" t="n">
+        <v>8088</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B987" t="s">
+        <v>7</v>
+      </c>
+      <c r="C987" t="s">
+        <v>7</v>
+      </c>
+      <c r="D987" t="s">
+        <v>8</v>
+      </c>
+      <c r="E987" t="s">
+        <v>9</v>
+      </c>
+      <c r="F987" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="G987" t="n">
+        <v>8032</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B988" t="s">
+        <v>7</v>
+      </c>
+      <c r="C988" t="s">
+        <v>7</v>
+      </c>
+      <c r="D988" t="s">
+        <v>8</v>
+      </c>
+      <c r="E988" t="s">
+        <v>9</v>
+      </c>
+      <c r="F988" s="1" t="n">
+        <v>45913</v>
+      </c>
+      <c r="G988" t="n">
+        <v>8513</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B989" t="s">
+        <v>7</v>
+      </c>
+      <c r="C989" t="s">
+        <v>7</v>
+      </c>
+      <c r="D989" t="s">
+        <v>8</v>
+      </c>
+      <c r="E989" t="s">
+        <v>9</v>
+      </c>
+      <c r="F989" s="1" t="n">
+        <v>45914</v>
+      </c>
+      <c r="G989" t="n">
+        <v>6925</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B990" t="s">
+        <v>7</v>
+      </c>
+      <c r="C990" t="s">
+        <v>7</v>
+      </c>
+      <c r="D990" t="s">
+        <v>8</v>
+      </c>
+      <c r="E990" t="s">
+        <v>9</v>
+      </c>
+      <c r="F990" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="G990" t="n">
+        <v>5362</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B991" t="s">
+        <v>7</v>
+      </c>
+      <c r="C991" t="s">
+        <v>7</v>
+      </c>
+      <c r="D991" t="s">
+        <v>8</v>
+      </c>
+      <c r="E991" t="s">
+        <v>9</v>
+      </c>
+      <c r="F991" s="1" t="n">
+        <v>45916</v>
+      </c>
+      <c r="G991" t="n">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B992" t="s">
+        <v>7</v>
+      </c>
+      <c r="C992" t="s">
+        <v>7</v>
+      </c>
+      <c r="D992" t="s">
+        <v>8</v>
+      </c>
+      <c r="E992" t="s">
+        <v>9</v>
+      </c>
+      <c r="F992" s="1" t="n">
+        <v>45917</v>
+      </c>
+      <c r="G992" t="n">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B993" t="s">
+        <v>7</v>
+      </c>
+      <c r="C993" t="s">
+        <v>7</v>
+      </c>
+      <c r="D993" t="s">
+        <v>8</v>
+      </c>
+      <c r="E993" t="s">
+        <v>9</v>
+      </c>
+      <c r="F993" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="G993" t="n">
+        <v>6215</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B994" t="s">
+        <v>7</v>
+      </c>
+      <c r="C994" t="s">
+        <v>7</v>
+      </c>
+      <c r="D994" t="s">
+        <v>8</v>
+      </c>
+      <c r="E994" t="s">
+        <v>9</v>
+      </c>
+      <c r="F994" s="1" t="n">
+        <v>45919</v>
+      </c>
+      <c r="G994" t="n">
+        <v>6042</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B995" t="s">
+        <v>7</v>
+      </c>
+      <c r="C995" t="s">
+        <v>7</v>
+      </c>
+      <c r="D995" t="s">
+        <v>8</v>
+      </c>
+      <c r="E995" t="s">
+        <v>9</v>
+      </c>
+      <c r="F995" s="1" t="n">
+        <v>45920</v>
+      </c>
+      <c r="G995" t="n">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B996" t="s">
+        <v>7</v>
+      </c>
+      <c r="C996" t="s">
+        <v>7</v>
+      </c>
+      <c r="D996" t="s">
+        <v>8</v>
+      </c>
+      <c r="E996" t="s">
+        <v>9</v>
+      </c>
+      <c r="F996" s="1" t="n">
+        <v>45921</v>
+      </c>
+      <c r="G996" t="n">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B997" t="s">
+        <v>7</v>
+      </c>
+      <c r="C997" t="s">
+        <v>7</v>
+      </c>
+      <c r="D997" t="s">
+        <v>8</v>
+      </c>
+      <c r="E997" t="s">
+        <v>9</v>
+      </c>
+      <c r="F997" s="1" t="n">
+        <v>45922</v>
+      </c>
+      <c r="G997" t="n">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B998" t="s">
+        <v>7</v>
+      </c>
+      <c r="C998" t="s">
+        <v>7</v>
+      </c>
+      <c r="D998" t="s">
+        <v>8</v>
+      </c>
+      <c r="E998" t="s">
+        <v>9</v>
+      </c>
+      <c r="F998" s="1" t="n">
+        <v>45923</v>
+      </c>
+      <c r="G998" t="n">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B999" t="s">
+        <v>7</v>
+      </c>
+      <c r="C999" t="s">
+        <v>7</v>
+      </c>
+      <c r="D999" t="s">
+        <v>8</v>
+      </c>
+      <c r="E999" t="s">
+        <v>9</v>
+      </c>
+      <c r="F999" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="G999" t="n">
+        <v>7489</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1000" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>6376</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1001" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1002" s="1" t="n">
+        <v>45927</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1003" s="1" t="n">
+        <v>45928</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1004" s="1" t="n">
+        <v>45929</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1005" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1006" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1007" s="1" t="n">
+        <v>45932</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1008" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="G1008"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1009" s="1" t="n">
+        <v>45934</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1010" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1011" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1012" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1012" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1013" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1014" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1015" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1015" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1016" s="1" t="n">
+        <v>45941</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1017" s="1" t="n">
+        <v>45942</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1018" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1019" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1020" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1021" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1022" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1023" s="1" t="n">
+        <v>45948</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1024" s="1" t="n">
+        <v>45949</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1025" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1026" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1027" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1028" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1029" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1030" s="1" t="n">
+        <v>45955</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1031" s="1" t="n">
+        <v>45956</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1032" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1033" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1034" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1035" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1036" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1037" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1038" s="1" t="n">
+        <v>45963</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1039" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1040" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1041" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1042" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1043" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1044" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1045" s="1" t="n">
+        <v>45970</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1046" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1047" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1048" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1049" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1050" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1051" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1052" s="1" t="n">
+        <v>45977</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1053" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1054" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1055" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1056" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1057" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1058" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1059" s="1" t="n">
+        <v>45984</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1060" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1061" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1062" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1063" s="1" t="n">
+        <v>45988</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1064" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1065" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1066" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1067" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1068" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1069" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1070" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1071" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1072" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1073" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1074" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1075" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1076" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1077" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1078" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1079" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1080" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1081" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1082" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1083" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1084" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1085" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1086" s="1" t="n">
+        <v>46011</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1087" s="1" t="n">
+        <v>46012</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1088" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1089" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1090" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1091" s="1" t="n">
+        <v>46016</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1092" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1093" s="1" t="n">
+        <v>46018</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1094" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1095" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1096" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1097" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
